--- a/src/attributions/attributions_ig_traj_194.xlsx
+++ b/src/attributions/attributions_ig_traj_194.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,22 +999,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.09743256086901915</v>
+        <v>0.08310473855381474</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2622399841521429</v>
+        <v>0.09040833694876943</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00303967780147252</v>
+        <v>-0.05188805760246934</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1023,136 +1023,136 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0157858522608739</v>
+        <v>0.0147909712417176</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2500957338607838</v>
+        <v>-0.0357111240507839</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002467049924387657</v>
+        <v>-0.01108821478867174</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1032613445660863</v>
+        <v>0.03494758772762276</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.02328870688007144</v>
+        <v>-0.103294720109881</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.04642507234038794</v>
+        <v>0.04509803033059642</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.05884914754576637</v>
+        <v>-0.004117680654579643</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.008743753015760445</v>
+        <v>-0.003367156910360922</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.002596583407561699</v>
+        <v>-0.02909759724648091</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.04332689688553018</v>
+        <v>0.1325812178138995</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.03201138138282502</v>
+        <v>-0.03263391403441177</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07100016630325545</v>
+        <v>0.2239386230188607</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1663206817060559</v>
+        <v>0.2684937158327911</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09800526917072176</v>
+        <v>-0.01679659038432532</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.0003144551746630985</v>
+        <v>0.0325630510023873</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1164,16 +1164,16 @@
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.02341166372543108</v>
+        <v>-0.06735727090895623</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1037817066555361</v>
+        <v>0.04629051565699074</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03475721051285342</v>
+        <v>-0.08697581709747651</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,58 +1182,58 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.03593428771602011</v>
+        <v>-0.0665203775162627</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.0417328291051336</v>
+        <v>-0.09519770889778818</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.09108884403239019</v>
+        <v>-0.01425468879081647</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.05189477069328403</v>
+        <v>0.1173212588293836</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.02464001639811764</v>
+        <v>-0.1262285499463847</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.02992743296277599</v>
+        <v>0.001035333273410764</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1245,73 +1245,73 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03395303151392331</v>
+        <v>-0.1230938160772061</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.04222034789380898</v>
+        <v>-0.039151967280279</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01981383323074086</v>
+        <v>-0.01977418141346554</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01585140079057015</v>
+        <v>-0.09975679493810162</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.0266578807857839</v>
+        <v>0.1275901196966225</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.04226796836385542</v>
+        <v>-0.01762609288963083</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04930545569512913</v>
+        <v>-0.1220703066530953</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.04394995226766105</v>
+        <v>-0.03125412008731446</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01160994819653272</v>
+        <v>0.002178945546759009</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1320,31 +1320,31 @@
         <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.03230739597374906</v>
+        <v>-0.07412197208844906</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01908407623220925</v>
+        <v>0.04991857102314958</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04476623474884861</v>
+        <v>-0.001025596346589713</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>-0</v>
@@ -1353,19 +1353,19 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.02352762696697234</v>
+        <v>-0.009056439802921867</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.03397899713890748</v>
+        <v>-0.003056253476135042</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.02038357453964971</v>
+        <v>0.02408943052125734</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1377,52 +1377,52 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.05521342815995583</v>
+        <v>0.03884915730507584</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.01748659847869833</v>
+        <v>0.1176821303376579</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.03069589261656241</v>
+        <v>0.2133064490614419</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.04440782764334671</v>
+        <v>-0.09898630695097269</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0778287514814467</v>
+        <v>0.182296899930484</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.02568372809262882</v>
+        <v>0.02743802449973464</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1431,19 +1431,19 @@
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.05103484235418234</v>
+        <v>-0.0746768264207264</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.03681046101146412</v>
+        <v>0.02512606833094732</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.03196449392776059</v>
+        <v>-0.002746465310802393</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -1452,112 +1452,112 @@
         <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04619994784946117</v>
+        <v>-0.1531582643667552</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.03583138226814911</v>
+        <v>-0.009294791703679384</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0215542075157635</v>
+        <v>-0.01367133153259309</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.008348946584245088</v>
+        <v>-0.1307223520739874</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.009127320605065678</v>
+        <v>-0.02675347069503169</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.005088268726051238</v>
+        <v>0.08888481578956443</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.004157056812444756</v>
+        <v>-0.14416521701166</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.02284002279882993</v>
+        <v>0.200348028228206</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.01101548204690669</v>
+        <v>-0.03295386290859655</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03916468553119062</v>
+        <v>-0.04888366613282569</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.02405378880385655</v>
+        <v>0.0005608381703619836</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,25 +1568,25 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.04827798893135966</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.01518512035855134</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.03169788587774038</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1595,10 +1595,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.01828369603387181</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,52 +1607,52 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>-0.003368828824250066</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.005466010238832689</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.03001374055776627</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.0231562293646631</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.02168668088482216</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.007917912327790225</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1661,94 +1661,94 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.04265087933271717</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.03221426024283348</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.01458479137905445</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.04617610811805454</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0.01067159194773347</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0.02939906114281968</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.05734533844098663</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.03934609523755614</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.02034101586319943</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.03063400701751628</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0.003708703224555256</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -1757,88 +1757,88 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.06015768739389209</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.03407616928245331</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.0006963393684679694</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0.0112195262510863</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.03222971247811676</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.01756291649819528</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.03014067080737252</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.02331097897003661</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.01595448150138562</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0.006341455320119909</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,43 +1847,43 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.05557910004961764</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.01212988424925601</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.02413145922473277</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.03547110555516587</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.02345349829880575</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.004316423660533492</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -1904,49 +1904,49 @@
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.03014541294646235</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.005479235923316748</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0.003704243817747472</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.03192225713547182</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.01073436217083632</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.009965399784808357</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
@@ -1955,52 +1955,52 @@
         <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>-0.00473924599660567</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.04500972999508079</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.03445489183370429</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.02163707179744963</v>
       </c>
       <c r="EK3" t="n">
         <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.007312369023261766</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.02420843104373924</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
@@ -2012,22 +2012,22 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.03430678859582195</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0.004287452886612158</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.03371686766155263</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
@@ -2039,52 +2039,52 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.03970514816834093</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.02485422203166932</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.05066915609385618</v>
       </c>
       <c r="FH3" t="n">
         <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>-0.01441616221569568</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0.00213123203009962</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.00631481552942744</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
@@ -2093,45 +2093,8011 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>-0.02783072487641097</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.015026148633806</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.02727251148949113</v>
       </c>
       <c r="FZ3" t="n">
         <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.02336917711083855</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3827665924663091</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06522246110835137</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.2768355251572067</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2064428623817476</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.0238456377067439</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.04474394118646838</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1153642001643249</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.1191604085247303</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.1277442508830805</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.132646163684042</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0387695743690929</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.1149006197518145</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1455013547618035</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.01374480761705609</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.2256212672572171</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.6978190273283044</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.2697768455857925</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.3633048100662626</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.1360536117962973</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.06053646996283717</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.1701248542315081</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.04129146176214286</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.1163341047102528</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.1439220101794011</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.2540725767153242</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.09869266957400674</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.2624447906176562</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.2838475265490725</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.05482208513679845</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1768908909976367</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.2961915192492241</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.06023581169610676</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.1613290127276087</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.2680537303245056</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.04670032335655826</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1488019095165297</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-0.1127783666858438</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-0.06978145062611883</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.1308242428626018</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-0.117000110414488</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>-0.001251940370408</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.03954027789855375</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.1398869355882332</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.03035784804289184</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.1492745931554651</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>-0.1295137576840679</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.075957590839193</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.1612078610616276</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>-0.1745134722290684</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.182689745252186</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.2046257987955727</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>-0.2613091677916803</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.1103268084619194</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1555532103102157</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>-0.1504322189709761</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>-0.04250756222719893</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.2620555431733647</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>-0.01945430781425148</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.03164152151879818</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.04735236813433847</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>-0.134003646650604</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.1331542078497562</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.4384039956195732</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.04538908935132382</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.1947707082608084</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2513439976623449</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.0419055576159388</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.179775150367137</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1825440131773233</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1326231924272519</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.02700077935624414</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.02269550045015923</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.2778832793021365</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.02513236962102311</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.228786921313327</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.1315506959575716</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.1540621430702762</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.8956952660816797</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.1920154189571465</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.2095329064918507</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.05076223510397743</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.09314335914194206</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.1289309439910103</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.05717839056177397</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.1344999374153151</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.1517300671884729</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.4290051398469107</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.007958140148571767</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.2626600987080719</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.2628866912740395</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0.04390733275078211</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.1797208278592962</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.2121162707226801</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.09299239009770417</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.0009462475321775621</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.238299787557628</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.04274363208764671</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.1913888460343736</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.05164177102471366</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.1046624927010084</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.03712806607285291</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.09242909978446429</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.002193784235796319</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0.02036501438912705</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.07818231143801664</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.04593172216098722</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.1197872149082266</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.080699767320279</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.1403731439581098</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.0679282696626886</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.1552889686109828</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.185037963554127</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.04687577696272491</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0.2659874299308909</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0.08316727539627608</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.1591612669932086</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0.2346648057422885</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.05207123207672158</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.2700689620411183</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0.03035356408874377</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0.002638939551354952</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.1293249028959451</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>-0.1303794041592252</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.0926186146769131</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.4259240844977518</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02325259711149527</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.2357813871788519</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3020736418611836</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.04700047301443963</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.1871292576712967</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1440740692610349</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.1473351965869563</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.02128206674656486</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.09177809979474559</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.2881343925364444</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.1172662198644401</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2025058567965067</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1138712563717369</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.1364594091371077</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.7339104754674338</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.1954230750219034</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.2626690975176362</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.01243914821593659</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.08935147235246191</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.1891719239598585</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.0609280269262114</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.1100647208661755</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.05583373506679393</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.3571168955767911</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.06018561053082604</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.1711114828854337</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.2469854321452575</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.02371025852815394</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1663637513113202</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.2144639499679488</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.1209775925889791</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.02398997726088449</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.2235520882042806</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>-0.03651660587776627</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.1660380292472896</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.07208929714864197</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.05079464727650149</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>-0.00184999396516972</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.1010521737815442</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0.0325141766650266</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.0711807409532972</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.04075960312369289</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.1069817591457412</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.09436576008219717</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.06448907104491809</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0.08329975713285012</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.07479002815229335</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0.1204417764112646</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0.09566703187398093</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.113458753860636</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0.2542825379077033</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0.05218010090534052</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.1423791064533729</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0.2784378441396697</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.1313843581192732</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.2624832739023138</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>-0.04791751191951735</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.002792798619521941</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.1663757894560932</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>-0.06497788477635628</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.02622915352466389</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5119102734620014</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.07459283593156114</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.02811411422245428</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.1226913887424731</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.5085404455387585</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.1595161553284121</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.1044894789207739</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.06179721789400646</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1413421587672724</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1434690937105414</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.1418236495355908</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.01251347641193619</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.01572528633176841</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.2891957355881525</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.229704242835473</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.06558378510719831</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2490723801463645</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.09101553964427603</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.07410241254534554</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.1734804054902633</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.7447966258471567</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.009627314842746112</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.298333832964767</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.1552271123116166</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.07825980859227695</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.1506721154484284</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.07238187566313616</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.06384637555014611</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.06307531946009515</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.01000371463347163</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.1449258821540388</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-0.003345793317380514</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.3574906659729383</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.0620348871789611</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.0889847889299286</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.1275410026604259</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.2301617720293408</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.06410648263769868</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.03724247445554827</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.05456411145682984</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.1695260559268879</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.1333949391093027</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.1376528156777883</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.06983854618062595</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.1991022902077415</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.06765254579148221</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.02125140835394585</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.05673559716689788</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.03324187653436318</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.0130642882253049</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.3131555434321701</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0.003823724107825384</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.1332702869746346</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.0196641989568893</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.07445492767940215</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0737031063214427</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.147855382314605</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.03502286539648919</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>-0.06993763785523043</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>-0.03764148773016745</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.06865252182845862</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.08095844473853893</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>-0.001666582856452425</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.008217359638360049</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.07305494775873619</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>-0.03024953573102541</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.03225420595340783</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.1501144903331058</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.2468019469213336</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.06124521938781195</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.01964466715465906</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.03821392924890588</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.1162440079991649</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.11500064642372</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.03963205610838949</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.1428247748803974</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>-0.1957695795711718</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.3013127627160383</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.01143937384384452</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.109223591063631</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.1448290485983767</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>-0.1006074055350331</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0.01937730013568087</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.238961158249</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.01621626532689649</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.215698691833053</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.1642786857023738</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0539938408027779</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1498192799456233</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.09250741647785143</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.005991025351602938</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.03397014972306713</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.05077835533231128</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.1557369139536982</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.04800979965170532</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.1144453559233114</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.07998475135721246</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.1410559288515709</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.2968500868239511</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.07489308395981019</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.1189639219364783</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.1025441145713944</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.2080913621062747</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.1369969166126893</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.02878882107026522</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.04368537745758733</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0.04467187405244637</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.2184991790668978</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.004271522980598305</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.08513152425187674</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.1255847658170457</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>-0.01049187220397186</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0.08320392431305056</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.08394446478923714</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.1708271323030337</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.05864175839431174</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.1194494801937152</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.005453496673305293</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0.07868424703598739</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.003256450189991945</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.06774831515585876</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0.01200270045128158</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.016784326646979</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.02639496560650748</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0.02590312053084436</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>-0.005621351121560628</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.03237888066052686</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.01116584641356237</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.06026917246943747</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.005851109187019248</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>-0.0122091824938285</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.1038414493790883</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.07700131782067751</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.1126644908508743</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.1345708743556027</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0.00282445851945151</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0.06679861431653838</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.1506127654110247</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.05028086661366655</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0.09382152697030378</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.1268773200606509</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.003303276351113327</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0.08288601663707666</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.09520569439790905</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.01819785778274406</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.491767413737112</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.009709867113094241</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.2431786965210316</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6316525952191819</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.1392843353914876</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1982767980040329</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.1250903903244557</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.0003448818803299358</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1052833383147869</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.008375186205488605</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.07011827411587897</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.05571839476122591</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1422156905207082</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.06460569189677982</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.07999960663684222</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.6587008043839068</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.2522304522874511</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.2714495943249056</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.1746781606573581</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.003790200711980096</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.02423411462128557</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.001607280047622419</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.07419388358712171</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.03211741077777853</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.4001682158251685</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.0268493771319939</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.138401433707689</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.2141630117101869</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.02322062994529397</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.0862227776316654</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.09481783950663464</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.08183779708420305</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.03933531447453385</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.2019946592039993</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.01488198229285261</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.1020558446508183</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.009536439045192248</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.01593646258162737</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.07189957042075333</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.0696898762971544</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.01823300728046297</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.07740230647602303</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.1316260421402424</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.06863147766280282</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>-0.09547324932019342</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.1198386945516544</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.04560696921898525</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.026394224658826</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.08951748017971926</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.0114732179245419</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>-0.03983245381944273</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.2335535756294134</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.001239501381015964</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.1011557440820771</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.1174067069753251</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>-0.01281575562559527</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.1037807413401616</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.2145251297919641</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>-0.04756804326272752</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>-0.007928796056339945</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.1029856525690179</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.05113667331309434</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.4782815955224255</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1435215279772306</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0895994081987538</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.6273752135586758</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2950827062286282</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1967318583408129</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.06817523078245118</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.01684148636256588</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.008996871032175932</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.03830504311207556</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1667803674149911</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.262483150316759</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1774589574907677</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.05165517057107236</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.2916620396914731</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.283628566268589</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.1818948375101984</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.04616690612004751</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.05660104569558545</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.005530514363629451</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.1588687063281517</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.1581041006799179</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.1079810587582977</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.002044237755174478</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.2182235551507777</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.0849635451486782</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.00229788063085726</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.2413504394086344</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0.07373545075727592</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.0005468613986733546</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.1161385091020462</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0.137058259138777</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.0854847128518456</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.2516131352312672</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0.07618181200368075</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.03214622703501956</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.1741365253411854</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-0.02630469104044088</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.0006343040407488659</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.09582967514791894</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>-0.06340978073097117</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.04255529446039405</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.04441902928564788</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.07031645217848789</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>-0.0198557432065995</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.2824157268337482</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0.0499538331469043</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.04865882304719942</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.1707167129853674</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0.03567192987989543</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.01440081166870209</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.2807194931226091</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0.09250071840641259</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.0004398324501113159</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.1058673328357576</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.1335995164212805</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.08330987196921266</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.2197885685123973</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.008441848319834015</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>-0.07024281221436443</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.226356842976614</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0.0002259311968922013</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3563346611196312</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.03092164831917627</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1426984252606821</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5036583725829984</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.1219332840142775</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.2176796523836552</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1064887658080962</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1166618233662825</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.005090410387975141</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.02931597959110936</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.2716371709374638</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.004549947446162852</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.03627142449193518</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.03902280683020567</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.0179704578611553</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.4830067608289389</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.2471306261364534</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.1030859309087518</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.02640743229741034</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.01826023118805718</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.08055430902221697</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.05420754045649814</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.07284421821868936</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.03856732649621976</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.2599856884467435</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.07364203894135758</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.09421125771368159</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.1098733076809664</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.02944543385110552</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.04753346200453771</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.132883428025923</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.1103401426896391</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.1006350723349099</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.1101429362917546</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.008845732805488119</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.06877497437296268</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.04971666937476797</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.168019676363107</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.04964933054648572</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.01092191807312633</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.05045557676934236</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.06265048639325359</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.02029626083507293</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>-0.07606006179769176</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.02755687738840463</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.04202635601058043</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.02215210337803252</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.009410661920081128</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.01312609594229622</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.01706506412837016</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.1215373664251312</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.1296503996940592</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.000249308693892745</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.03831841965707554</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.1922076591772191</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0.09426401307233671</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.109675009652774</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.009855611703085876</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>-0.0251904100577068</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.05046906775903426</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.03420563764413689</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.05732790399884384</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.3958643794029042</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.02084509152020293</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.1446385525758582</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.4986440986933964</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.1279690718404325</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.2041604031644494</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.08982252365081479</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.0746323075620289</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.009302112134788276</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.03024932641232912</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.2307873373409146</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.01709925190226669</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.04035664814959713</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0.02778306521480335</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.0001885847210065052</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.3938336471289925</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.2563008768056509</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.1024042275531773</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.00252955785861262</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.002904869744809502</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.04804601829997016</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.03959616992019722</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.04865757265505019</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-0.02422771510152101</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.2209306048771014</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0.05304717578285637</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>-0.09802608447146666</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0.1034167076342855</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.02809609202439048</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.05187316016624946</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0.1324474891003564</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>0.1474936523834096</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0.06768225135802683</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-0.1010686269832201</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0.015331665117897</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0.07164908613476234</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>-0.08033913368697386</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0.1956340256185488</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0.06007360194547549</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-0.01837878589909518</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>-0.03498485093664613</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0.02766281593663096</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>-0.006562249680281331</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>-0.06639004196760329</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0.0166167110461417</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>-0.04669363257947479</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>0.01152574949112689</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0.004292513796186449</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0.04251452547465764</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0.0155457864232985</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0.0860015087308605</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>-0.1214162651914464</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>0.002555874606952007</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0.04479780620918175</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0.1511574967464079</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>-0.08862515265782175</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>0.109636536573462</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0.00150547842735951</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>-0.009248608646502012</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>-0.0243058301229967</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>-0.02878331499979738</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0.0646616299022493</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG17" t="n">
         <v>0</v>
       </c>
     </row>
